--- a/Ejercicios/Levels/B2/PARTE 10/Script para tabla levels_respuestas parte 10.xlsx
+++ b/Ejercicios/Levels/B2/PARTE 10/Script para tabla levels_respuestas parte 10.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Webs\english-practice\Ejercicios\Levels\B2\PARTE 10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAFBF087-DB74-49E6-9F10-0D33992260D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD55E017-96FA-45BF-8487-29B690BE4177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2A9E9770-0A60-448A-A645-1DDB5E014A2D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{2A9E9770-0A60-448A-A645-1DDB5E014A2D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="examen 1" sheetId="1" r:id="rId1"/>
+    <sheet name="examen 2,3,4 y 5" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="50">
   <si>
     <t>id</t>
   </si>
@@ -190,7 +191,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,6 +202,13 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -226,9 +234,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1026,4 +1037,503 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16D43702-07BA-41AD-B62F-2E82AE45A78D}">
+  <dimension ref="C4:G44"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="6" width="39.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="3:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="3:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="3:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="3:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="3:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="3:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="3:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" t="s">
+        <v>6</v>
+      </c>
+      <c r="G11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="3:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="3:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="3:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" t="s">
+        <v>6</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="3:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" t="s">
+        <v>6</v>
+      </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="3:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" t="s">
+        <v>6</v>
+      </c>
+      <c r="G18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G20">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F21" t="s">
+        <v>6</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" t="s">
+        <v>6</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23" t="s">
+        <v>6</v>
+      </c>
+      <c r="G23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" t="s">
+        <v>6</v>
+      </c>
+      <c r="G24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" t="s">
+        <v>6</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F26" t="s">
+        <v>6</v>
+      </c>
+      <c r="G26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" t="s">
+        <v>6</v>
+      </c>
+      <c r="G27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G28">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D30" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F30" t="s">
+        <v>6</v>
+      </c>
+      <c r="G30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F31" t="s">
+        <v>6</v>
+      </c>
+      <c r="G31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G32">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F33" t="s">
+        <v>6</v>
+      </c>
+      <c r="G33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F34" t="s">
+        <v>6</v>
+      </c>
+      <c r="G34">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F35" t="s">
+        <v>6</v>
+      </c>
+      <c r="G35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D36" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G36">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E37" s="1"/>
+    </row>
+    <row r="38" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E38" s="1"/>
+    </row>
+    <row r="39" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E39" s="1"/>
+    </row>
+    <row r="40" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E40" s="1"/>
+    </row>
+    <row r="41" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E41" s="1"/>
+    </row>
+    <row r="42" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E42" s="1"/>
+    </row>
+    <row r="43" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E43" s="1"/>
+    </row>
+    <row r="44" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E44" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>